--- a/output/2026-09-08_15_Croazia_Krapinsko-zagorska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-08_15_Croazia_Krapinsko-zagorska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Confermata su fininfo.hr/poslovna.hr/moja-djelatnost.hr: distributore autorizzato Bosch, Tyrolit, Dremel, Elektroda Zagreb, Lacuna. Telefono confermato da fonte pubblica.</t>
+          <t>Confermata su fininfo.hr/poslovna.hr/moja-djelatnost.hr: distributore autorizzato Bosch, Tyrolit, Dremel, Elektroda Zagreb, Lacuna. Telefono confermato da fonte pubblica. [DUPLICATO — vedi anche: 2026-09-08_06_Croazia_Krapinsko-zagorska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vendita e assistenza utensili Bosch, Makita, Stayer. Telefono confermato esattamente da fonte pubblica.</t>
+          <t>Vendita e assistenza utensili Bosch, Makita, Stayer. Telefono confermato esattamente da fonte pubblica. [DUPLICATO — vedi anche: 2026-09-07_23_Croazia_Zagrebacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -620,7 +620,6 @@
           <t>049 638 108</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Distributore regionale leader ricambi/attrezzature per officina, oltre 300 marchi. Coerenza col settore metalworking solo parziale (focus aftermarket auto).</t>

--- a/output/2026-09-08_15_Croazia_Krapinsko-zagorska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-08_15_Croazia_Krapinsko-zagorska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
